--- a/output/pdf_financials_xlsx/APN.xlsx
+++ b/output/pdf_financials_xlsx/APN.xlsx
@@ -5789,18 +5789,16 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.163968</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.163968</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.504359</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>2.536658</v>
       </c>
     </row>
     <row r="93">
@@ -9344,7 +9342,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10978,7 +10980,11 @@
           <t>Reserves 2,504,359</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12070,7 +12076,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/APN.xlsx
+++ b/output/pdf_financials_xlsx/APN.xlsx
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.010813</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.014478</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1005,31 +1005,31 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005432</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002825</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000101</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.01146</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.005075</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00876</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.282598</v>
+        <v>-0.293411</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.205475</v>
+        <v>-0.219953</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.27674</v>
+        <v>-0.282172</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1879,22 +1879,22 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.373793</v>
+        <v>-1.373833</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.211692</v>
+        <v>-2.211793</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.832126</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.319996</v>
+        <v>-2.331456</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.454603</v>
+        <v>-2.459678</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.564032</v>
+        <v>-1.572792</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-1.664104</v>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.282598</v>
+        <v>-0.293411</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.205475</v>
+        <v>-0.219953</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.27674</v>
+        <v>-0.282172</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.373793</v>
+        <v>-1.373833</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.211692</v>
+        <v>-2.211793</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.832126</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.319996</v>
+        <v>-2.331456</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.352204</v>
+        <v>-2.357279</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.282336</v>
+        <v>-1.291096</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-1.664104</v>
@@ -2235,13 +2235,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015801</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.349807</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.148991</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2264,27 +2264,25 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.058327</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.048437</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.029766</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.459246</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.459246</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.097374</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.226759</v>
       </c>
     </row>
     <row r="35">
@@ -2353,13 +2351,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.015801</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.349807</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.148991</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2382,27 +2380,25 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.058327</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.048437</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.029766</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.459246</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.459246</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.097374</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.226759</v>
       </c>
     </row>
     <row r="37">
@@ -3057,13 +3053,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.059752</v>
+        <v>0.043951</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.351782</v>
+        <v>0.001975</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.16849</v>
+        <v>0.019499</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3086,22 +3082,22 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.235878</v>
+        <v>0.177551</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.141164</v>
+        <v>0.092727</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.076262</v>
+        <v>0.046496</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.678654</v>
+        <v>0.219408</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.678654</v>
+        <v>0.219408</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.469076</v>
+        <v>0.371702</v>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
@@ -8184,7 +8180,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9776,7 +9772,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -26876,7 +26872,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -30088,7 +30084,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">

--- a/output/pdf_financials_xlsx/APN.xlsx
+++ b/output/pdf_financials_xlsx/APN.xlsx
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.07022</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.102399</v>
+        <v>0.060934</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0.281696</v>
@@ -1998,10 +1998,10 @@
         <v>-0.832126</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.331456</v>
+        <v>-2.261236</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.357279</v>
+        <v>-2.398744</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.291096</v>
@@ -6209,10 +6209,10 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.07022</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.060934</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -16104,7 +16104,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -26784,7 +26788,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -26841,7 +26849,7 @@
         </is>
       </c>
       <c r="P223" s="5" t="n">
-        <v>-0.060934</v>
+        <v>0.060934</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -27884,7 +27892,11 @@
           <t>Depreciation of right-of-use asset (note 8)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -27936,10 +27948,10 @@
         </is>
       </c>
       <c r="O236" s="5" t="n">
-        <v>-0.07022</v>
+        <v>0.07022</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>-0.060934</v>
+        <v>0.060934</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
